--- a/ML/Linear Reg1/data1.xlsx
+++ b/ML/Linear Reg1/data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tamzidislam/Documents/MyMac/ML_BASICS/ML/Linear Reg1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C89A6C3-D201-B14A-9626-17EAA5C3B370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A11DF7C-1B2D-4F49-92FD-E71E1A8B9B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17060" xr2:uid="{0450A035-D595-C746-A43C-579D6C64F9D4}"/>
   </bookViews>
@@ -425,7 +425,7 @@
         <v>2600</v>
       </c>
       <c r="C2">
-        <v>550000</v>
+        <v>518000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -433,10 +433,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="C3">
-        <v>565000</v>
+        <v>523000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -444,10 +444,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="C4">
-        <v>610000</v>
+        <v>578000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -455,10 +455,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>3600</v>
+        <v>3200</v>
       </c>
       <c r="C5">
-        <v>680000</v>
+        <v>635000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -466,10 +466,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="C6">
-        <v>725000</v>
+        <v>601000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -477,10 +477,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="C7">
-        <v>755000</v>
+        <v>628000</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -488,10 +488,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4400</v>
+        <v>3800</v>
       </c>
       <c r="C8">
-        <v>785000</v>
+        <v>718000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -499,10 +499,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="C9">
-        <v>800000</v>
+        <v>717000</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -510,10 +510,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="C10">
-        <v>830000</v>
+        <v>701000</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -521,10 +521,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="C11">
-        <v>860000</v>
+        <v>763000</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -532,10 +532,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5200</v>
+        <v>4600</v>
       </c>
       <c r="C12">
-        <v>890000</v>
+        <v>755000</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -543,10 +543,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="C13">
-        <v>915000</v>
+        <v>782000</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -554,10 +554,10 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="C14">
-        <v>940000</v>
+        <v>833000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -565,10 +565,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="C15">
-        <v>970000</v>
+        <v>785000</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -576,10 +576,10 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>6000</v>
+        <v>5400</v>
       </c>
       <c r="C16">
-        <v>1000000</v>
+        <v>819000</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -587,10 +587,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>6200</v>
+        <v>5600</v>
       </c>
       <c r="C17">
-        <v>1025000</v>
+        <v>886000</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -598,10 +598,10 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>6400</v>
+        <v>5800</v>
       </c>
       <c r="C18">
-        <v>1055000</v>
+        <v>898000</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -609,10 +609,10 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="C19">
-        <v>1080000</v>
+        <v>971000</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -620,10 +620,10 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="C20">
-        <v>1110000</v>
+        <v>955000</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -631,10 +631,10 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="C21">
-        <v>1135000</v>
+        <v>965000</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -642,10 +642,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>7200</v>
+        <v>6600</v>
       </c>
       <c r="C22">
-        <v>1165000</v>
+        <v>1092000</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -653,10 +653,10 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>7400</v>
+        <v>6800</v>
       </c>
       <c r="C23">
-        <v>1190000</v>
+        <v>1060000</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -664,10 +664,10 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="C24">
-        <v>1220000</v>
+        <v>1097000</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -675,10 +675,10 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>7800</v>
+        <v>7200</v>
       </c>
       <c r="C25">
-        <v>1245000</v>
+        <v>1072000</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -686,10 +686,10 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>8000</v>
+        <v>7400</v>
       </c>
       <c r="C26">
-        <v>1275000</v>
+        <v>1130000</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -697,10 +697,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="C27">
-        <v>1300000</v>
+        <v>1180000</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -708,10 +708,10 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>8400</v>
+        <v>7800</v>
       </c>
       <c r="C28">
-        <v>1330000</v>
+        <v>1163000</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -719,10 +719,10 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>8600</v>
+        <v>8000</v>
       </c>
       <c r="C29">
-        <v>1355000</v>
+        <v>1243000</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -730,10 +730,10 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>8800</v>
+        <v>8200</v>
       </c>
       <c r="C30">
-        <v>1385000</v>
+        <v>1236000</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -741,10 +741,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>9000</v>
+        <v>8400</v>
       </c>
       <c r="C31">
-        <v>1410000</v>
+        <v>1274000</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -752,10 +752,10 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>9200</v>
+        <v>8600</v>
       </c>
       <c r="C32">
-        <v>1440000</v>
+        <v>1290000</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -763,10 +763,10 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>9400</v>
+        <v>8800</v>
       </c>
       <c r="C33">
-        <v>1465000</v>
+        <v>1403000</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -774,10 +774,10 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>9600</v>
+        <v>9000</v>
       </c>
       <c r="C34">
-        <v>1495000</v>
+        <v>1365000</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -785,10 +785,10 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>9800</v>
+        <v>9200</v>
       </c>
       <c r="C35">
-        <v>1520000</v>
+        <v>1355000</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -796,10 +796,10 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>10000</v>
+        <v>9400</v>
       </c>
       <c r="C36">
-        <v>1550000</v>
+        <v>1448000</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -807,10 +807,10 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>10200</v>
+        <v>9600</v>
       </c>
       <c r="C37">
-        <v>1575000</v>
+        <v>1403000</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -818,10 +818,10 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>10400</v>
+        <v>9800</v>
       </c>
       <c r="C38">
-        <v>1605000</v>
+        <v>1480000</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -829,10 +829,10 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>10600</v>
+        <v>10000</v>
       </c>
       <c r="C39">
-        <v>1630000</v>
+        <v>1431000</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -840,10 +840,10 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>10800</v>
+        <v>10200</v>
       </c>
       <c r="C40">
-        <v>1660000</v>
+        <v>1481000</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -851,10 +851,10 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>11000</v>
+        <v>10400</v>
       </c>
       <c r="C41">
-        <v>1685000</v>
+        <v>1561000</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -862,10 +862,10 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>11200</v>
+        <v>10600</v>
       </c>
       <c r="C42">
-        <v>1715000</v>
+        <v>1607000</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -873,10 +873,10 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>11400</v>
+        <v>10800</v>
       </c>
       <c r="C43">
-        <v>1740000</v>
+        <v>1614000</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -884,10 +884,10 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>11600</v>
+        <v>11000</v>
       </c>
       <c r="C44">
-        <v>1770000</v>
+        <v>1631000</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -895,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>11800</v>
+        <v>11200</v>
       </c>
       <c r="C45">
-        <v>1795000</v>
+        <v>1651000</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -906,10 +906,10 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>12000</v>
+        <v>11400</v>
       </c>
       <c r="C46">
-        <v>1825000</v>
+        <v>1637000</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -917,10 +917,10 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>12200</v>
+        <v>11600</v>
       </c>
       <c r="C47">
-        <v>1850000</v>
+        <v>1691000</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -928,10 +928,10 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>12400</v>
+        <v>11800</v>
       </c>
       <c r="C48">
-        <v>1880000</v>
+        <v>1727000</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -939,10 +939,10 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>12600</v>
+        <v>12000</v>
       </c>
       <c r="C49">
-        <v>1905000</v>
+        <v>1807000</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -950,10 +950,10 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>12800</v>
+        <v>12200</v>
       </c>
       <c r="C50">
-        <v>1935000</v>
+        <v>1809000</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -961,10 +961,10 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>13000</v>
+        <v>12400</v>
       </c>
       <c r="C51">
-        <v>1960000</v>
+        <v>1762000</v>
       </c>
     </row>
   </sheetData>
